--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.64400219470117</v>
+        <v>4.97965035663894</v>
       </c>
       <c r="D2" t="n">
-        <v>30.58601860631879</v>
+        <v>4.970228023526804</v>
       </c>
       <c r="E2" t="n">
-        <v>9.996568682309146</v>
+        <v>1.624442410875236</v>
       </c>
       <c r="F2" t="n">
-        <v>10.10195113312899</v>
+        <v>1.64156705913346</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.58007593759311</v>
+        <v>4.156762339858881</v>
       </c>
       <c r="D3" t="n">
-        <v>25.40106841209712</v>
+        <v>4.127673616965783</v>
       </c>
       <c r="E3" t="n">
-        <v>9.996568682309146</v>
+        <v>1.624442410875236</v>
       </c>
       <c r="F3" t="n">
-        <v>10.10195113312899</v>
+        <v>1.64156705913346</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.59307747196347</v>
+        <v>4.158875089194064</v>
       </c>
       <c r="D4" t="n">
-        <v>25.33371080416544</v>
+        <v>4.116728005676884</v>
       </c>
       <c r="E4" t="n">
-        <v>9.996568682309146</v>
+        <v>1.624442410875236</v>
       </c>
       <c r="F4" t="n">
-        <v>10.10195113312899</v>
+        <v>1.64156705913346</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.29958565115142</v>
+        <v>4.598682668312106</v>
       </c>
       <c r="D5" t="n">
-        <v>28.10385216062343</v>
+        <v>4.566875976101307</v>
       </c>
       <c r="E5" t="n">
-        <v>9.996568682309146</v>
+        <v>1.624442410875236</v>
       </c>
       <c r="F5" t="n">
-        <v>10.10195113312899</v>
+        <v>1.64156705913346</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.81072334859397</v>
+        <v>5.819242544146521</v>
       </c>
       <c r="D6" t="n">
-        <v>36.03106990758847</v>
+        <v>5.855048859983127</v>
       </c>
       <c r="E6" t="n">
-        <v>9.996568682309146</v>
+        <v>1.624442410875236</v>
       </c>
       <c r="F6" t="n">
-        <v>10.10195113312899</v>
+        <v>1.64156705913346</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.35454069927455</v>
+        <v>5.420112863632115</v>
       </c>
       <c r="D7" t="n">
-        <v>33.51321792136108</v>
+        <v>5.445897912221176</v>
       </c>
       <c r="E7" t="n">
-        <v>9.996568682309146</v>
+        <v>1.624442410875236</v>
       </c>
       <c r="F7" t="n">
-        <v>10.10195113312899</v>
+        <v>1.64156705913346</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.60821378991868</v>
+        <v>9.198834740861786</v>
       </c>
       <c r="D8" t="n">
-        <v>56.70008592761754</v>
+        <v>9.213763963237851</v>
       </c>
       <c r="E8" t="n">
-        <v>9.996568682309146</v>
+        <v>1.624442410875236</v>
       </c>
       <c r="F8" t="n">
-        <v>10.10195113312899</v>
+        <v>1.64156705913346</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
